--- a/final_template/output/samsung_electronics_2025/Samsung_Electronics_2025_EBX_Q_consultant_safe_v4_KO.xlsx
+++ b/final_template/output/samsung_electronics_2025/Samsung_Electronics_2025_EBX_Q_consultant_safe_v4_KO.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="consultant_safe_v4" sheetId="1" r:id="Rc4c138cac76940e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="consultant_safe_v4" sheetId="1" r:id="R0dad42cce3d5499f"/>
   </x:sheets>
 </x:workbook>
 </file>
